--- a/access/samples/status_update_sample.xlsx
+++ b/access/samples/status_update_sample.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -458,17 +458,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EBUXSL2079418826</t>
+          <t>EBUXSL2079600001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>حائل</t>
+          <t>المجاردة</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>التسليم النهائي</t>
+          <t>جاهزة للالتقاط</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,7 +480,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EBUXSL2079602026</t>
+          <t>EBUXSL2079600002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,90 +490,90 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>جاهزة للالتقاط</t>
+          <t>استلام من العميل</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ثانوية المجاردة - مسارات - M174001</t>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EBUXSL2079500001</t>
+          <t>EBUXSL2079600003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>حائل</t>
+          <t>المجاردة</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>استلام من العميل</t>
+          <t>التسليم النهائي</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>متوسطة حائل - مسارات - M174100</t>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EBUXSL2079500002</t>
+          <t>EBUXSL2079600004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>حائل</t>
+          <t>المجاردة</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>قيد التوصيل</t>
+          <t>التسليم النهائي</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>متوسطة حائل - مسارات - M174100</t>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EBUXSL2079500003</t>
+          <t>EBUXSL2079600005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>أبها</t>
+          <t>المجاردة</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>التسليم النهائي</t>
+          <t>قيد التوصيل</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ثانوية أبها - مسارات - M174200</t>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EBUXSL2079999999</t>
+          <t>EBUXSL2079600006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>الرياض</t>
+          <t>المجاردة</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -583,34 +583,100 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>مدرسة غير مسجلة - M999999</t>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EBUXSL2079500003</t>
+          <t>EBUXSL2079700001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>أبها</t>
+          <t>حائل</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>جاهزة للالتقاط</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>متوسطة حائل - مسارات - M174100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EBUXSL2079700002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>حائل</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>التسليم النهائي</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ثانوية أبها - مسارات - M174200</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>متوسطة حائل - مسارات - M174100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EBUXSL2079999999</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>الرياض</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>التسليم النهائي</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>مدرسة غير مسجلة - M999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EBUXSL2079600004</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>المجاردة</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>التسليم النهائي</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ثانوية منار العلم الأهلية - مسارات - M174562</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>